--- a/inputs/acceptance_cases/stage2_absolute_out_of_envelope.xlsx
+++ b/inputs/acceptance_cases/stage2_absolute_out_of_envelope.xlsx
@@ -479,7 +479,7 @@
         <v>44569.3125</v>
       </c>
       <c r="C4" t="n">
-        <v>532</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5">
@@ -490,7 +490,7 @@
         <v>44569.32291666666</v>
       </c>
       <c r="C5" t="n">
-        <v>511</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         <v>44569.34375</v>
       </c>
       <c r="C7" t="n">
-        <v>511</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8">
@@ -534,7 +534,7 @@
         <v>44569.36458333334</v>
       </c>
       <c r="C9" t="n">
-        <v>511</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10">
@@ -556,7 +556,7 @@
         <v>44569.38541666666</v>
       </c>
       <c r="C11" t="n">
-        <v>516.5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12">
@@ -567,7 +567,7 @@
         <v>44569.39583333334</v>
       </c>
       <c r="C12" t="n">
-        <v>511</v>
+        <v>500</v>
       </c>
     </row>
     <row r="13">
@@ -600,7 +600,7 @@
         <v>44569.42708333334</v>
       </c>
       <c r="C15" t="n">
-        <v>505.5</v>
+        <v>533</v>
       </c>
     </row>
     <row r="16">
@@ -611,7 +611,7 @@
         <v>44569.4375</v>
       </c>
       <c r="C16" t="n">
-        <v>511</v>
+        <v>533</v>
       </c>
     </row>
     <row r="17">
@@ -622,7 +622,7 @@
         <v>44569.44791666666</v>
       </c>
       <c r="C17" t="n">
-        <v>511</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18">
@@ -633,7 +633,7 @@
         <v>44569.45833333334</v>
       </c>
       <c r="C18" t="n">
-        <v>511</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19">
@@ -644,7 +644,7 @@
         <v>44569.46875</v>
       </c>
       <c r="C19" t="n">
-        <v>505.5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="20">
@@ -655,7 +655,7 @@
         <v>44569.47916666666</v>
       </c>
       <c r="C20" t="n">
-        <v>505.5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21">
@@ -743,7 +743,7 @@
         <v>44569.3125</v>
       </c>
       <c r="C28" t="n">
-        <v>505.5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="29">
@@ -798,7 +798,7 @@
         <v>44569.36458333334</v>
       </c>
       <c r="C33" t="n">
-        <v>516.5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="34">
@@ -809,7 +809,7 @@
         <v>44569.375</v>
       </c>
       <c r="C34" t="n">
-        <v>516.5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="35">
@@ -831,7 +831,7 @@
         <v>44569.39583333334</v>
       </c>
       <c r="C36" t="n">
-        <v>505.5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="37">
@@ -842,7 +842,7 @@
         <v>44569.40625</v>
       </c>
       <c r="C37" t="n">
-        <v>505.5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="38">
@@ -853,7 +853,7 @@
         <v>44569.41666666666</v>
       </c>
       <c r="C38" t="n">
-        <v>516.5</v>
+        <v>533</v>
       </c>
     </row>
     <row r="39">
@@ -864,7 +864,7 @@
         <v>44569.42708333334</v>
       </c>
       <c r="C39" t="n">
-        <v>516.5</v>
+        <v>533</v>
       </c>
     </row>
     <row r="40">
@@ -875,7 +875,7 @@
         <v>44569.4375</v>
       </c>
       <c r="C40" t="n">
-        <v>516.5</v>
+        <v>533</v>
       </c>
     </row>
     <row r="41">
@@ -886,7 +886,7 @@
         <v>44569.44791666666</v>
       </c>
       <c r="C41" t="n">
-        <v>516.5</v>
+        <v>533</v>
       </c>
     </row>
     <row r="42">
@@ -897,7 +897,7 @@
         <v>44569.45833333334</v>
       </c>
       <c r="C42" t="n">
-        <v>511</v>
+        <v>500</v>
       </c>
     </row>
     <row r="43">
@@ -919,7 +919,7 @@
         <v>44569.47916666666</v>
       </c>
       <c r="C44" t="n">
-        <v>505.5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="45">
@@ -1029,7 +1029,7 @@
         <v>44569.33333333334</v>
       </c>
       <c r="C54" t="n">
-        <v>505.5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="55">
@@ -1051,7 +1051,7 @@
         <v>44569.35416666666</v>
       </c>
       <c r="C56" t="n">
-        <v>511</v>
+        <v>500</v>
       </c>
     </row>
     <row r="57">
@@ -1062,7 +1062,7 @@
         <v>44569.36458333334</v>
       </c>
       <c r="C57" t="n">
-        <v>516.5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="58">
@@ -1073,7 +1073,7 @@
         <v>44569.375</v>
       </c>
       <c r="C58" t="n">
-        <v>511</v>
+        <v>500</v>
       </c>
     </row>
     <row r="59">
@@ -1084,7 +1084,7 @@
         <v>44569.38541666666</v>
       </c>
       <c r="C59" t="n">
-        <v>505.5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="60">
@@ -1106,7 +1106,7 @@
         <v>44569.40625</v>
       </c>
       <c r="C61" t="n">
-        <v>516.5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="62">
@@ -1117,7 +1117,7 @@
         <v>44569.41666666666</v>
       </c>
       <c r="C62" t="n">
-        <v>516.5</v>
+        <v>533</v>
       </c>
     </row>
     <row r="63">
@@ -1128,7 +1128,7 @@
         <v>44569.42708333334</v>
       </c>
       <c r="C63" t="n">
-        <v>505.5</v>
+        <v>533</v>
       </c>
     </row>
     <row r="64">
@@ -1139,7 +1139,7 @@
         <v>44569.4375</v>
       </c>
       <c r="C64" t="n">
-        <v>516.5</v>
+        <v>533</v>
       </c>
     </row>
     <row r="65">
@@ -1150,7 +1150,7 @@
         <v>44569.44791666666</v>
       </c>
       <c r="C65" t="n">
-        <v>516.5</v>
+        <v>533</v>
       </c>
     </row>
     <row r="66">
@@ -1161,7 +1161,7 @@
         <v>44569.45833333334</v>
       </c>
       <c r="C66" t="n">
-        <v>516.5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="67">
@@ -1172,7 +1172,7 @@
         <v>44569.46875</v>
       </c>
       <c r="C67" t="n">
-        <v>505.5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="68">
@@ -1194,7 +1194,7 @@
         <v>44569.48958333334</v>
       </c>
       <c r="C69" t="n">
-        <v>505.5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="70">
